--- a/xlsx/物品数据.xlsx
+++ b/xlsx/物品数据.xlsx
@@ -264,17 +264,25 @@
           <t>AIha</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>255.0</v>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>255.0</t>
+        </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -328,17 +336,25 @@
           <t>AIha</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>255.0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.0</v>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>255.0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -392,8 +408,10 @@
           <t>AIha</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>1.0</v>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -447,17 +465,25 @@
           <t>AIha</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>255.0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>255.0</v>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>255.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>255.0</t>
+        </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -511,17 +537,25 @@
           <t>AIha</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>255.0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.0</v>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>255.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -575,17 +609,25 @@
           <t>AIha</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>255.0</v>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>255.0</t>
+        </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -639,17 +681,25 @@
           <t>AIha</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>255.0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.0</v>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>255.0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -703,8 +753,10 @@
           <t>AIha</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>1.0</v>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -758,17 +810,25 @@
           <t>AIha</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>255.0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>255.0</v>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>255.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>255.0</t>
+        </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -822,17 +882,25 @@
           <t>AIha</t>
         </is>
       </c>
-      <c r="J12" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>255.0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.0</v>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>255.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -886,17 +954,25 @@
           <t>AIha</t>
         </is>
       </c>
-      <c r="J13" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>255.0</v>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>255.0</t>
+        </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -950,17 +1026,25 @@
           <t>AIha</t>
         </is>
       </c>
-      <c r="J14" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>255.0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.0</v>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>255.0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1014,8 +1098,10 @@
           <t>AIha</t>
         </is>
       </c>
-      <c r="J15" t="n">
-        <v>1.0</v>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1069,17 +1155,25 @@
           <t>AIha</t>
         </is>
       </c>
-      <c r="J16" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>255.0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>255.0</v>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>255.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>255.0</t>
+        </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1133,17 +1227,25 @@
           <t>AIha</t>
         </is>
       </c>
-      <c r="J17" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>255.0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.0</v>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>255.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>

--- a/xlsx/物品数据.xlsx
+++ b/xlsx/物品数据.xlsx
@@ -69,14 +69,11 @@
     <col min="9" max="9" width="19.53125" customWidth="true"/>
     <col min="10" max="10" width="63.640625" customWidth="true"/>
     <col min="11" max="11" width="12.3828125" customWidth="true"/>
-    <col min="12" max="12" width="9.31640625" customWidth="true"/>
-    <col min="13" max="13" width="11.6640625" customWidth="true"/>
-    <col min="14" max="14" width="16.6328125" customWidth="true"/>
-    <col min="15" max="15" width="11.61328125" customWidth="true"/>
-    <col min="16" max="16" width="11.61328125" customWidth="true"/>
-    <col min="17" max="17" width="11.8125" customWidth="true"/>
-    <col min="18" max="18" width="19.96484375" customWidth="true"/>
-    <col min="19" max="19" width="70.3125" customWidth="true"/>
+    <col min="12" max="12" width="11.61328125" customWidth="true"/>
+    <col min="13" max="13" width="11.61328125" customWidth="true"/>
+    <col min="14" max="14" width="11.8125" customWidth="true"/>
+    <col min="15" max="15" width="19.96484375" customWidth="true"/>
+    <col min="16" max="16" width="70.3125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -137,40 +134,25 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>缩放</t>
+          <t>颜色值(蓝)</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>主动使用</t>
+          <t>颜色值(红)</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>可以被抵押</t>
+          <t>颜色值(绿)</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>颜色值(蓝)</t>
+          <t>CD间隔组</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
-        <is>
-          <t>颜色值(红)</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>颜色值(绿)</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>CD间隔组</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
         <is>
           <t>编辑器附加数据</t>
         </is>
@@ -234,40 +216,25 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>scale</t>
+          <t>colorB</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>usable</t>
+          <t>colorR</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>pawnable</t>
+          <t>colorG</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>colorB</t>
+          <t>cooldownID</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
-        <is>
-          <t>colorR</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>colorG</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>cooldownID</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
         <is>
           <t>W2LObject</t>
         </is>
@@ -314,32 +281,13 @@
           <t>Objects\InventoryItems\tome\tome.mdl</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>AIha</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="L3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0</v>
       </c>
       <c r="P3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>255.0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
         <is>
           <t>"XC":"技能书学习到QWER栏位.xlsx  【技能书学习到QWER栏位.iobj.ts】  "</t>
         </is>
@@ -386,32 +334,13 @@
           <t>Objects\InventoryItems\tome\tome.mdl</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>AIha</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>255.0</t>
-        </is>
+      <c r="M4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0</v>
       </c>
       <c r="P4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
         <is>
           <t>"XC":"技能书学习到QWER栏位.xlsx  【技能书学习到QWER栏位.iobj.ts】  "</t>
         </is>
@@ -458,17 +387,7 @@
           <t>Objects\InventoryItems\tome\tome.mdl</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>AIha</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>"XC":"技能书学习到QWER栏位.xlsx  【技能书学习到QWER栏位.iobj.ts】  "</t>
         </is>
@@ -515,32 +434,10 @@
           <t>Objects\InventoryItems\tome\tome.mdl</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>AIha</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="L6" t="n">
+        <v>0.0</v>
       </c>
       <c r="P6" t="inlineStr">
-        <is>
-          <t>255.0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>255.0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
         <is>
           <t>"XC":"技能书学习到QWER栏位.xlsx  【技能书学习到QWER栏位.iobj.ts】  "</t>
         </is>
@@ -587,32 +484,13 @@
           <t>Objects\InventoryItems\tome\tome.mdl</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>AIha</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="L7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0</v>
       </c>
       <c r="P7" t="inlineStr">
-        <is>
-          <t>255.0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
         <is>
           <t>"XC":"技能书学习到QWER栏位.xlsx  【技能书学习到QWER栏位.iobj.ts】  "</t>
         </is>
@@ -659,32 +537,13 @@
           <t>Objects\InventoryItems\tome\tome.mdl</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>AIha</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="L8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0</v>
       </c>
       <c r="P8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>255.0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
         <is>
           <t>"XC":"技能书学习到QWER栏位.xlsx  【技能书学习到QWER栏位.iobj.ts】  "</t>
         </is>
@@ -731,32 +590,13 @@
           <t>Objects\InventoryItems\tome\tome.mdl</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>AIha</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>255.0</t>
-        </is>
+      <c r="M9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0</v>
       </c>
       <c r="P9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
         <is>
           <t>"XC":"技能书学习到QWER栏位.xlsx  【技能书学习到QWER栏位.iobj.ts】  "</t>
         </is>
@@ -803,17 +643,7 @@
           <t>Objects\InventoryItems\tome\tome.mdl</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>AIha</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>"XC":"技能书学习到QWER栏位.xlsx  【技能书学习到QWER栏位.iobj.ts】  "</t>
         </is>
@@ -860,32 +690,10 @@
           <t>Objects\InventoryItems\tome\tome.mdl</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>AIha</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="L11" t="n">
+        <v>0.0</v>
       </c>
       <c r="P11" t="inlineStr">
-        <is>
-          <t>255.0</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>255.0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
         <is>
           <t>"XC":"技能书学习到QWER栏位.xlsx  【技能书学习到QWER栏位.iobj.ts】  "</t>
         </is>
@@ -932,32 +740,13 @@
           <t>Objects\InventoryItems\tome\tome.mdl</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>AIha</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="L12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.0</v>
       </c>
       <c r="P12" t="inlineStr">
-        <is>
-          <t>255.0</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
         <is>
           <t>"XC":"技能书学习到QWER栏位.xlsx  【技能书学习到QWER栏位.iobj.ts】  "</t>
         </is>
@@ -1004,32 +793,13 @@
           <t>Objects\InventoryItems\tome\tome.mdl</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>AIha</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="L13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.0</v>
       </c>
       <c r="P13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>255.0</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
         <is>
           <t>"XC":"技能书学习到QWER栏位.xlsx  【技能书学习到QWER栏位.iobj.ts】  "</t>
         </is>
@@ -1076,32 +846,13 @@
           <t>Objects\InventoryItems\tome\tome.mdl</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>AIha</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>255.0</t>
-        </is>
+      <c r="M14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.0</v>
       </c>
       <c r="P14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
         <is>
           <t>"XC":"技能书学习到QWER栏位.xlsx  【技能书学习到QWER栏位.iobj.ts】  "</t>
         </is>
@@ -1148,17 +899,7 @@
           <t>Objects\InventoryItems\tome\tome.mdl</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>AIha</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>"XC":"技能书学习到QWER栏位.xlsx  【技能书学习到QWER栏位.iobj.ts】  "</t>
         </is>
@@ -1205,32 +946,10 @@
           <t>Objects\InventoryItems\tome\tome.mdl</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>AIha</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="L16" t="n">
+        <v>0.0</v>
       </c>
       <c r="P16" t="inlineStr">
-        <is>
-          <t>255.0</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>255.0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
         <is>
           <t>"XC":"技能书学习到QWER栏位.xlsx  【技能书学习到QWER栏位.iobj.ts】  "</t>
         </is>
@@ -1277,32 +996,13 @@
           <t>Objects\InventoryItems\tome\tome.mdl</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>AIha</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="L17" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.0</v>
       </c>
       <c r="P17" t="inlineStr">
-        <is>
-          <t>255.0</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
         <is>
           <t>"XC":"技能书学习到QWER栏位.xlsx  【技能书学习到QWER栏位.iobj.ts】  "</t>
         </is>
@@ -1331,7 +1031,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1345,13 +1045,7 @@
           <t>q0va</t>
         </is>
       </c>
-      <c r="M18" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>q0va</t>
         </is>
@@ -1380,7 +1074,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1394,13 +1088,7 @@
           <t>q0vc</t>
         </is>
       </c>
-      <c r="M19" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>q0vc</t>
         </is>
@@ -1429,7 +1117,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1443,13 +1131,7 @@
           <t>q0ve</t>
         </is>
       </c>
-      <c r="M20" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>q0ve</t>
         </is>
@@ -1478,7 +1160,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1492,13 +1174,7 @@
           <t>q0vg</t>
         </is>
       </c>
-      <c r="M21" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>q0vg</t>
         </is>
@@ -1527,7 +1203,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1541,13 +1217,7 @@
           <t>q0vi</t>
         </is>
       </c>
-      <c r="M22" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>q0vi</t>
         </is>
@@ -1576,7 +1246,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1590,13 +1260,7 @@
           <t>q0vk</t>
         </is>
       </c>
-      <c r="M23" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>q0vk</t>
         </is>
@@ -1625,7 +1289,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1639,13 +1303,7 @@
           <t>q0vm</t>
         </is>
       </c>
-      <c r="M24" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>q0vm</t>
         </is>
@@ -1674,7 +1332,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1688,13 +1346,7 @@
           <t>q0vo</t>
         </is>
       </c>
-      <c r="M25" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>q0vo</t>
         </is>
@@ -1723,7 +1375,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1737,13 +1389,7 @@
           <t>q0vq</t>
         </is>
       </c>
-      <c r="M26" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>q0vq</t>
         </is>
@@ -1772,7 +1418,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -1786,13 +1432,7 @@
           <t>q0vs</t>
         </is>
       </c>
-      <c r="M27" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>q0vs</t>
         </is>
@@ -1821,7 +1461,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1835,13 +1475,7 @@
           <t>q0vu</t>
         </is>
       </c>
-      <c r="M28" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>q0vu</t>
         </is>
@@ -1870,7 +1504,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1884,13 +1518,7 @@
           <t>q100</t>
         </is>
       </c>
-      <c r="M29" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>q100</t>
         </is>
@@ -1919,7 +1547,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1933,13 +1561,7 @@
           <t>q102</t>
         </is>
       </c>
-      <c r="M30" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>q102</t>
         </is>
@@ -1968,7 +1590,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -1982,13 +1604,7 @@
           <t>q104</t>
         </is>
       </c>
-      <c r="M31" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>q104</t>
         </is>
@@ -2017,7 +1633,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2031,13 +1647,7 @@
           <t>q106</t>
         </is>
       </c>
-      <c r="M32" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>q106</t>
         </is>
@@ -2066,7 +1676,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2080,13 +1690,7 @@
           <t>q108</t>
         </is>
       </c>
-      <c r="M33" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>q108</t>
         </is>
@@ -2115,7 +1719,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2129,13 +1733,7 @@
           <t>q10a</t>
         </is>
       </c>
-      <c r="M34" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>q10a</t>
         </is>
@@ -2164,7 +1762,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2178,13 +1776,7 @@
           <t>q10c</t>
         </is>
       </c>
-      <c r="M35" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>q10c</t>
         </is>
@@ -2213,7 +1805,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2227,13 +1819,7 @@
           <t>q10e</t>
         </is>
       </c>
-      <c r="M36" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>q10e</t>
         </is>
@@ -2262,7 +1848,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2276,13 +1862,7 @@
           <t>q10g</t>
         </is>
       </c>
-      <c r="M37" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>q10g</t>
         </is>
@@ -2311,7 +1891,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2325,13 +1905,7 @@
           <t>q10i</t>
         </is>
       </c>
-      <c r="M38" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>q10i</t>
         </is>
@@ -2360,7 +1934,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -2374,13 +1948,7 @@
           <t>q10k</t>
         </is>
       </c>
-      <c r="M39" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>q10k</t>
         </is>
@@ -2409,7 +1977,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2423,13 +1991,7 @@
           <t>q10m</t>
         </is>
       </c>
-      <c r="M40" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>q10m</t>
         </is>
@@ -2458,7 +2020,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -2472,13 +2034,7 @@
           <t>q10o</t>
         </is>
       </c>
-      <c r="M41" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>q10o</t>
         </is>
@@ -2507,7 +2063,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2521,13 +2077,7 @@
           <t>q10q</t>
         </is>
       </c>
-      <c r="M42" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>q10q</t>
         </is>
@@ -2556,7 +2106,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -2570,13 +2120,7 @@
           <t>q10s</t>
         </is>
       </c>
-      <c r="M43" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>q10s</t>
         </is>
@@ -2605,7 +2149,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -2619,13 +2163,7 @@
           <t>q10u</t>
         </is>
       </c>
-      <c r="M44" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>q10u</t>
         </is>
@@ -2654,7 +2192,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -2668,13 +2206,7 @@
           <t>q110</t>
         </is>
       </c>
-      <c r="M45" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>q110</t>
         </is>
@@ -2703,7 +2235,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -2717,13 +2249,7 @@
           <t>q112</t>
         </is>
       </c>
-      <c r="M46" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>q112</t>
         </is>
@@ -2752,7 +2278,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -2766,13 +2292,7 @@
           <t>q114</t>
         </is>
       </c>
-      <c r="M47" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>q114</t>
         </is>
@@ -2801,7 +2321,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -2815,13 +2335,7 @@
           <t>q116</t>
         </is>
       </c>
-      <c r="M48" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>q116</t>
         </is>
@@ -2850,7 +2364,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -2864,13 +2378,7 @@
           <t>q118</t>
         </is>
       </c>
-      <c r="M49" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>q118</t>
         </is>
@@ -2899,7 +2407,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -2913,13 +2421,7 @@
           <t>q11a</t>
         </is>
       </c>
-      <c r="M50" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N50" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>q11a</t>
         </is>
@@ -2948,7 +2450,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -2962,13 +2464,7 @@
           <t>q11c</t>
         </is>
       </c>
-      <c r="M51" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>q11c</t>
         </is>
@@ -2997,7 +2493,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -3011,13 +2507,7 @@
           <t>q11e</t>
         </is>
       </c>
-      <c r="M52" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N52" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>q11e</t>
         </is>
@@ -3046,7 +2536,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -3060,13 +2550,7 @@
           <t>q11g</t>
         </is>
       </c>
-      <c r="M53" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>q11g</t>
         </is>
@@ -3095,7 +2579,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -3109,13 +2593,7 @@
           <t>q11i</t>
         </is>
       </c>
-      <c r="M54" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>q11i</t>
         </is>
@@ -3144,7 +2622,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -3158,13 +2636,7 @@
           <t>q11k</t>
         </is>
       </c>
-      <c r="M55" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N55" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>q11k</t>
         </is>
@@ -3193,7 +2665,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3207,13 +2679,7 @@
           <t>q11m</t>
         </is>
       </c>
-      <c r="M56" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N56" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>q11m</t>
         </is>
@@ -3242,7 +2708,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -3256,13 +2722,7 @@
           <t>q11o</t>
         </is>
       </c>
-      <c r="M57" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>q11o</t>
         </is>
@@ -3291,7 +2751,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -3305,13 +2765,7 @@
           <t>q11q</t>
         </is>
       </c>
-      <c r="M58" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N58" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>q11q</t>
         </is>
@@ -3340,7 +2794,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -3354,13 +2808,7 @@
           <t>q11s</t>
         </is>
       </c>
-      <c r="M59" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>q11s</t>
         </is>
@@ -3389,7 +2837,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -3403,13 +2851,7 @@
           <t>q11u</t>
         </is>
       </c>
-      <c r="M60" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N60" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>q11u</t>
         </is>
@@ -3438,7 +2880,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -3452,13 +2894,7 @@
           <t>q120</t>
         </is>
       </c>
-      <c r="M61" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N61" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>q120</t>
         </is>
@@ -3487,7 +2923,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -3501,13 +2937,7 @@
           <t>q122</t>
         </is>
       </c>
-      <c r="M62" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N62" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>q122</t>
         </is>
@@ -3536,7 +2966,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -3550,13 +2980,7 @@
           <t>q124</t>
         </is>
       </c>
-      <c r="M63" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N63" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>q124</t>
         </is>
@@ -3585,7 +3009,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -3599,13 +3023,7 @@
           <t>q126</t>
         </is>
       </c>
-      <c r="M64" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N64" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>q126</t>
         </is>
@@ -3634,7 +3052,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -3648,13 +3066,7 @@
           <t>q128</t>
         </is>
       </c>
-      <c r="M65" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N65" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>q128</t>
         </is>
@@ -3683,7 +3095,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -3697,13 +3109,7 @@
           <t>q12a</t>
         </is>
       </c>
-      <c r="M66" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N66" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>q12a</t>
         </is>
@@ -3732,7 +3138,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -3746,13 +3152,7 @@
           <t>q12c</t>
         </is>
       </c>
-      <c r="M67" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N67" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>q12c</t>
         </is>
@@ -3781,7 +3181,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -3795,13 +3195,7 @@
           <t>q12e</t>
         </is>
       </c>
-      <c r="M68" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N68" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>q12e</t>
         </is>
@@ -3830,7 +3224,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -3844,13 +3238,7 @@
           <t>q12g</t>
         </is>
       </c>
-      <c r="M69" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N69" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>q12g</t>
         </is>
@@ -3879,7 +3267,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -3893,13 +3281,7 @@
           <t>q12i</t>
         </is>
       </c>
-      <c r="M70" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N70" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>q12i</t>
         </is>
@@ -3928,7 +3310,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -3942,13 +3324,7 @@
           <t>q12k</t>
         </is>
       </c>
-      <c r="M71" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N71" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>q12k</t>
         </is>
@@ -3977,7 +3353,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -3991,13 +3367,7 @@
           <t>q12m</t>
         </is>
       </c>
-      <c r="M72" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N72" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>q12m</t>
         </is>
@@ -4026,7 +3396,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -4040,13 +3410,7 @@
           <t>q12o</t>
         </is>
       </c>
-      <c r="M73" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N73" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R73" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>q12o</t>
         </is>
@@ -4075,7 +3439,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -4089,13 +3453,7 @@
           <t>q12q</t>
         </is>
       </c>
-      <c r="M74" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N74" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>q12q</t>
         </is>
@@ -4124,7 +3482,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -4138,13 +3496,7 @@
           <t>q12s</t>
         </is>
       </c>
-      <c r="M75" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N75" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>q12s</t>
         </is>
@@ -4173,7 +3525,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -4187,13 +3539,7 @@
           <t>q12u</t>
         </is>
       </c>
-      <c r="M76" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N76" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R76" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>q12u</t>
         </is>
@@ -4222,7 +3568,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -4236,13 +3582,7 @@
           <t>q130</t>
         </is>
       </c>
-      <c r="M77" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N77" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R77" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t>q130</t>
         </is>
@@ -4271,7 +3611,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -4285,13 +3625,7 @@
           <t>q132</t>
         </is>
       </c>
-      <c r="M78" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N78" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R78" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>q132</t>
         </is>
@@ -4320,7 +3654,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -4334,13 +3668,7 @@
           <t>q134</t>
         </is>
       </c>
-      <c r="M79" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N79" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R79" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>q134</t>
         </is>
@@ -4369,7 +3697,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -4383,13 +3711,7 @@
           <t>q136</t>
         </is>
       </c>
-      <c r="M80" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N80" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R80" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>q136</t>
         </is>
@@ -4418,7 +3740,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -4432,13 +3754,7 @@
           <t>q138</t>
         </is>
       </c>
-      <c r="M81" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N81" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R81" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>q138</t>
         </is>
@@ -4467,7 +3783,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -4481,13 +3797,7 @@
           <t>q13a</t>
         </is>
       </c>
-      <c r="M82" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N82" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R82" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>q13a</t>
         </is>
@@ -4516,7 +3826,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -4530,13 +3840,7 @@
           <t>q13c</t>
         </is>
       </c>
-      <c r="M83" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N83" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R83" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t>q13c</t>
         </is>
@@ -4565,7 +3869,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -4579,13 +3883,7 @@
           <t>q13e</t>
         </is>
       </c>
-      <c r="M84" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N84" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R84" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t>q13e</t>
         </is>
@@ -4614,7 +3912,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -4628,13 +3926,7 @@
           <t>q13g</t>
         </is>
       </c>
-      <c r="M85" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N85" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R85" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t>q13g</t>
         </is>
@@ -4663,7 +3955,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -4677,13 +3969,7 @@
           <t>q13i</t>
         </is>
       </c>
-      <c r="M86" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N86" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R86" t="inlineStr">
+      <c r="O86" t="inlineStr">
         <is>
           <t>q13i</t>
         </is>
@@ -4712,7 +3998,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -4726,13 +4012,7 @@
           <t>q13k</t>
         </is>
       </c>
-      <c r="M87" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N87" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R87" t="inlineStr">
+      <c r="O87" t="inlineStr">
         <is>
           <t>q13k</t>
         </is>
@@ -4761,7 +4041,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -4775,13 +4055,7 @@
           <t>q13m</t>
         </is>
       </c>
-      <c r="M88" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N88" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R88" t="inlineStr">
+      <c r="O88" t="inlineStr">
         <is>
           <t>q13m</t>
         </is>
@@ -4810,7 +4084,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -4824,13 +4098,7 @@
           <t>q13o</t>
         </is>
       </c>
-      <c r="M89" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N89" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R89" t="inlineStr">
+      <c r="O89" t="inlineStr">
         <is>
           <t>q13o</t>
         </is>
@@ -4859,7 +4127,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -4873,13 +4141,7 @@
           <t>q13q</t>
         </is>
       </c>
-      <c r="M90" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N90" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R90" t="inlineStr">
+      <c r="O90" t="inlineStr">
         <is>
           <t>q13q</t>
         </is>
@@ -4908,7 +4170,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -4922,13 +4184,7 @@
           <t>q13s</t>
         </is>
       </c>
-      <c r="M91" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N91" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R91" t="inlineStr">
+      <c r="O91" t="inlineStr">
         <is>
           <t>q13s</t>
         </is>
@@ -4957,7 +4213,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -4971,13 +4227,7 @@
           <t>q13u</t>
         </is>
       </c>
-      <c r="M92" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N92" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R92" t="inlineStr">
+      <c r="O92" t="inlineStr">
         <is>
           <t>q13u</t>
         </is>
@@ -5006,7 +4256,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -5020,13 +4270,7 @@
           <t>q140</t>
         </is>
       </c>
-      <c r="M93" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N93" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R93" t="inlineStr">
+      <c r="O93" t="inlineStr">
         <is>
           <t>q140</t>
         </is>
@@ -5055,7 +4299,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -5069,13 +4313,7 @@
           <t>q142</t>
         </is>
       </c>
-      <c r="M94" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N94" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R94" t="inlineStr">
+      <c r="O94" t="inlineStr">
         <is>
           <t>q142</t>
         </is>
@@ -5104,7 +4342,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -5118,13 +4356,7 @@
           <t>q144</t>
         </is>
       </c>
-      <c r="M95" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N95" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R95" t="inlineStr">
+      <c r="O95" t="inlineStr">
         <is>
           <t>q144</t>
         </is>
@@ -5153,7 +4385,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -5167,13 +4399,7 @@
           <t>q146</t>
         </is>
       </c>
-      <c r="M96" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N96" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R96" t="inlineStr">
+      <c r="O96" t="inlineStr">
         <is>
           <t>q146</t>
         </is>
@@ -5202,7 +4428,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -5216,13 +4442,7 @@
           <t>q148</t>
         </is>
       </c>
-      <c r="M97" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N97" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R97" t="inlineStr">
+      <c r="O97" t="inlineStr">
         <is>
           <t>q148</t>
         </is>
@@ -5251,7 +4471,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -5265,13 +4485,7 @@
           <t>q14a</t>
         </is>
       </c>
-      <c r="M98" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N98" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R98" t="inlineStr">
+      <c r="O98" t="inlineStr">
         <is>
           <t>q14a</t>
         </is>
@@ -5300,7 +4514,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -5314,13 +4528,7 @@
           <t>q14c</t>
         </is>
       </c>
-      <c r="M99" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N99" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R99" t="inlineStr">
+      <c r="O99" t="inlineStr">
         <is>
           <t>q14c</t>
         </is>
@@ -5349,7 +4557,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -5363,13 +4571,7 @@
           <t>q14e</t>
         </is>
       </c>
-      <c r="M100" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N100" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R100" t="inlineStr">
+      <c r="O100" t="inlineStr">
         <is>
           <t>q14e</t>
         </is>
@@ -5398,7 +4600,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -5412,13 +4614,7 @@
           <t>q14g</t>
         </is>
       </c>
-      <c r="M101" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N101" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R101" t="inlineStr">
+      <c r="O101" t="inlineStr">
         <is>
           <t>q14g</t>
         </is>
@@ -5447,7 +4643,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -5461,13 +4657,7 @@
           <t>q14i</t>
         </is>
       </c>
-      <c r="M102" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N102" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R102" t="inlineStr">
+      <c r="O102" t="inlineStr">
         <is>
           <t>q14i</t>
         </is>
@@ -5496,7 +4686,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -5510,13 +4700,7 @@
           <t>q14k</t>
         </is>
       </c>
-      <c r="M103" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N103" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R103" t="inlineStr">
+      <c r="O103" t="inlineStr">
         <is>
           <t>q14k</t>
         </is>
@@ -5545,7 +4729,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -5559,13 +4743,7 @@
           <t>q14m</t>
         </is>
       </c>
-      <c r="M104" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N104" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R104" t="inlineStr">
+      <c r="O104" t="inlineStr">
         <is>
           <t>q14m</t>
         </is>
@@ -5594,7 +4772,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -5608,13 +4786,7 @@
           <t>q14o</t>
         </is>
       </c>
-      <c r="M105" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N105" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R105" t="inlineStr">
+      <c r="O105" t="inlineStr">
         <is>
           <t>q14o</t>
         </is>
@@ -5643,7 +4815,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -5657,13 +4829,7 @@
           <t>q14q</t>
         </is>
       </c>
-      <c r="M106" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N106" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R106" t="inlineStr">
+      <c r="O106" t="inlineStr">
         <is>
           <t>q14q</t>
         </is>
@@ -5692,7 +4858,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -5706,13 +4872,7 @@
           <t>q14s</t>
         </is>
       </c>
-      <c r="M107" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N107" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R107" t="inlineStr">
+      <c r="O107" t="inlineStr">
         <is>
           <t>q14s</t>
         </is>
@@ -5741,7 +4901,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -5755,13 +4915,7 @@
           <t>q14u</t>
         </is>
       </c>
-      <c r="M108" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N108" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R108" t="inlineStr">
+      <c r="O108" t="inlineStr">
         <is>
           <t>q14u</t>
         </is>
@@ -5790,7 +4944,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -5804,13 +4958,7 @@
           <t>q150</t>
         </is>
       </c>
-      <c r="M109" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N109" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R109" t="inlineStr">
+      <c r="O109" t="inlineStr">
         <is>
           <t>q150</t>
         </is>
@@ -5839,7 +4987,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -5853,13 +5001,7 @@
           <t>q152</t>
         </is>
       </c>
-      <c r="M110" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N110" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R110" t="inlineStr">
+      <c r="O110" t="inlineStr">
         <is>
           <t>q152</t>
         </is>
@@ -5888,7 +5030,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -5902,13 +5044,7 @@
           <t>q154</t>
         </is>
       </c>
-      <c r="M111" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N111" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R111" t="inlineStr">
+      <c r="O111" t="inlineStr">
         <is>
           <t>q154</t>
         </is>
@@ -5937,7 +5073,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -5951,13 +5087,7 @@
           <t>q156</t>
         </is>
       </c>
-      <c r="M112" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N112" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R112" t="inlineStr">
+      <c r="O112" t="inlineStr">
         <is>
           <t>q156</t>
         </is>
@@ -5986,7 +5116,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -6000,13 +5130,7 @@
           <t>q158</t>
         </is>
       </c>
-      <c r="M113" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N113" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R113" t="inlineStr">
+      <c r="O113" t="inlineStr">
         <is>
           <t>q158</t>
         </is>
@@ -6035,7 +5159,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -6049,13 +5173,7 @@
           <t>q15a</t>
         </is>
       </c>
-      <c r="M114" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N114" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R114" t="inlineStr">
+      <c r="O114" t="inlineStr">
         <is>
           <t>q15a</t>
         </is>
@@ -6084,7 +5202,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -6098,13 +5216,7 @@
           <t>q15c</t>
         </is>
       </c>
-      <c r="M115" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N115" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R115" t="inlineStr">
+      <c r="O115" t="inlineStr">
         <is>
           <t>q15c</t>
         </is>
@@ -6133,7 +5245,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -6147,13 +5259,7 @@
           <t>q15e</t>
         </is>
       </c>
-      <c r="M116" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N116" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R116" t="inlineStr">
+      <c r="O116" t="inlineStr">
         <is>
           <t>q15e</t>
         </is>
@@ -6182,7 +5288,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -6196,13 +5302,7 @@
           <t>q15g</t>
         </is>
       </c>
-      <c r="M117" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N117" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R117" t="inlineStr">
+      <c r="O117" t="inlineStr">
         <is>
           <t>q15g</t>
         </is>
@@ -6231,7 +5331,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -6245,13 +5345,7 @@
           <t>q15i</t>
         </is>
       </c>
-      <c r="M118" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N118" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R118" t="inlineStr">
+      <c r="O118" t="inlineStr">
         <is>
           <t>q15i</t>
         </is>
@@ -6280,7 +5374,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -6294,13 +5388,7 @@
           <t>q15k</t>
         </is>
       </c>
-      <c r="M119" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N119" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R119" t="inlineStr">
+      <c r="O119" t="inlineStr">
         <is>
           <t>q15k</t>
         </is>
@@ -6329,7 +5417,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -6343,13 +5431,7 @@
           <t>q15m</t>
         </is>
       </c>
-      <c r="M120" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N120" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R120" t="inlineStr">
+      <c r="O120" t="inlineStr">
         <is>
           <t>q15m</t>
         </is>
@@ -6378,7 +5460,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -6392,13 +5474,7 @@
           <t>q15o</t>
         </is>
       </c>
-      <c r="M121" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N121" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R121" t="inlineStr">
+      <c r="O121" t="inlineStr">
         <is>
           <t>q15o</t>
         </is>
@@ -6427,7 +5503,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -6441,13 +5517,7 @@
           <t>q15q</t>
         </is>
       </c>
-      <c r="M122" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N122" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R122" t="inlineStr">
+      <c r="O122" t="inlineStr">
         <is>
           <t>q15q</t>
         </is>
@@ -6476,7 +5546,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -6490,13 +5560,7 @@
           <t>q15s</t>
         </is>
       </c>
-      <c r="M123" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N123" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R123" t="inlineStr">
+      <c r="O123" t="inlineStr">
         <is>
           <t>q15s</t>
         </is>
@@ -6525,7 +5589,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -6539,13 +5603,7 @@
           <t>q15u</t>
         </is>
       </c>
-      <c r="M124" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N124" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R124" t="inlineStr">
+      <c r="O124" t="inlineStr">
         <is>
           <t>q15u</t>
         </is>
@@ -6574,7 +5632,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -6588,13 +5646,7 @@
           <t>q160</t>
         </is>
       </c>
-      <c r="M125" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N125" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R125" t="inlineStr">
+      <c r="O125" t="inlineStr">
         <is>
           <t>q160</t>
         </is>
@@ -6623,7 +5675,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -6637,13 +5689,7 @@
           <t>q162</t>
         </is>
       </c>
-      <c r="M126" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N126" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R126" t="inlineStr">
+      <c r="O126" t="inlineStr">
         <is>
           <t>q162</t>
         </is>
@@ -6672,7 +5718,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -6686,13 +5732,7 @@
           <t>q164</t>
         </is>
       </c>
-      <c r="M127" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N127" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R127" t="inlineStr">
+      <c r="O127" t="inlineStr">
         <is>
           <t>q164</t>
         </is>
@@ -6721,7 +5761,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -6735,13 +5775,7 @@
           <t>q166</t>
         </is>
       </c>
-      <c r="M128" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N128" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R128" t="inlineStr">
+      <c r="O128" t="inlineStr">
         <is>
           <t>q166</t>
         </is>
@@ -6770,7 +5804,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -6784,13 +5818,7 @@
           <t>q168</t>
         </is>
       </c>
-      <c r="M129" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N129" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R129" t="inlineStr">
+      <c r="O129" t="inlineStr">
         <is>
           <t>q168</t>
         </is>
@@ -6819,7 +5847,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -6833,13 +5861,7 @@
           <t>q16a</t>
         </is>
       </c>
-      <c r="M130" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N130" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R130" t="inlineStr">
+      <c r="O130" t="inlineStr">
         <is>
           <t>q16a</t>
         </is>
@@ -6868,7 +5890,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -6882,13 +5904,7 @@
           <t>q16c</t>
         </is>
       </c>
-      <c r="M131" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N131" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R131" t="inlineStr">
+      <c r="O131" t="inlineStr">
         <is>
           <t>q16c</t>
         </is>
@@ -6917,7 +5933,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -6931,13 +5947,7 @@
           <t>q16e</t>
         </is>
       </c>
-      <c r="M132" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N132" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R132" t="inlineStr">
+      <c r="O132" t="inlineStr">
         <is>
           <t>q16e</t>
         </is>
@@ -6966,7 +5976,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -6980,13 +5990,7 @@
           <t>q16g</t>
         </is>
       </c>
-      <c r="M133" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N133" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R133" t="inlineStr">
+      <c r="O133" t="inlineStr">
         <is>
           <t>q16g</t>
         </is>
@@ -7015,7 +6019,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -7029,13 +6033,7 @@
           <t>q16i</t>
         </is>
       </c>
-      <c r="M134" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N134" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R134" t="inlineStr">
+      <c r="O134" t="inlineStr">
         <is>
           <t>q16i</t>
         </is>
@@ -7064,7 +6062,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -7078,13 +6076,7 @@
           <t>q16k</t>
         </is>
       </c>
-      <c r="M135" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N135" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R135" t="inlineStr">
+      <c r="O135" t="inlineStr">
         <is>
           <t>q16k</t>
         </is>
@@ -7113,7 +6105,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -7127,13 +6119,7 @@
           <t>q16m</t>
         </is>
       </c>
-      <c r="M136" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N136" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R136" t="inlineStr">
+      <c r="O136" t="inlineStr">
         <is>
           <t>q16m</t>
         </is>
@@ -7162,7 +6148,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -7176,13 +6162,7 @@
           <t>q16o</t>
         </is>
       </c>
-      <c r="M137" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N137" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R137" t="inlineStr">
+      <c r="O137" t="inlineStr">
         <is>
           <t>q16o</t>
         </is>
@@ -7211,7 +6191,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -7225,13 +6205,7 @@
           <t>q16q</t>
         </is>
       </c>
-      <c r="M138" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N138" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R138" t="inlineStr">
+      <c r="O138" t="inlineStr">
         <is>
           <t>q16q</t>
         </is>
@@ -7260,7 +6234,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -7274,13 +6248,7 @@
           <t>q16s</t>
         </is>
       </c>
-      <c r="M139" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N139" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R139" t="inlineStr">
+      <c r="O139" t="inlineStr">
         <is>
           <t>q16s</t>
         </is>
@@ -7309,7 +6277,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -7323,13 +6291,7 @@
           <t>q16u</t>
         </is>
       </c>
-      <c r="M140" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N140" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R140" t="inlineStr">
+      <c r="O140" t="inlineStr">
         <is>
           <t>q16u</t>
         </is>
@@ -7358,7 +6320,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -7372,13 +6334,7 @@
           <t>q170</t>
         </is>
       </c>
-      <c r="M141" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N141" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R141" t="inlineStr">
+      <c r="O141" t="inlineStr">
         <is>
           <t>q170</t>
         </is>
@@ -7407,7 +6363,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -7421,13 +6377,7 @@
           <t>q172</t>
         </is>
       </c>
-      <c r="M142" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N142" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R142" t="inlineStr">
+      <c r="O142" t="inlineStr">
         <is>
           <t>q172</t>
         </is>
@@ -7456,7 +6406,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -7470,13 +6420,7 @@
           <t>q174</t>
         </is>
       </c>
-      <c r="M143" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N143" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R143" t="inlineStr">
+      <c r="O143" t="inlineStr">
         <is>
           <t>q174</t>
         </is>
@@ -7505,7 +6449,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -7519,13 +6463,7 @@
           <t>q176</t>
         </is>
       </c>
-      <c r="M144" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N144" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R144" t="inlineStr">
+      <c r="O144" t="inlineStr">
         <is>
           <t>q176</t>
         </is>
@@ -7554,7 +6492,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -7568,13 +6506,7 @@
           <t>q178</t>
         </is>
       </c>
-      <c r="M145" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N145" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R145" t="inlineStr">
+      <c r="O145" t="inlineStr">
         <is>
           <t>q178</t>
         </is>
@@ -7603,7 +6535,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -7617,13 +6549,7 @@
           <t>q17a</t>
         </is>
       </c>
-      <c r="M146" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N146" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R146" t="inlineStr">
+      <c r="O146" t="inlineStr">
         <is>
           <t>q17a</t>
         </is>
@@ -7652,7 +6578,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -7666,13 +6592,7 @@
           <t>q17c</t>
         </is>
       </c>
-      <c r="M147" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N147" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R147" t="inlineStr">
+      <c r="O147" t="inlineStr">
         <is>
           <t>q17c</t>
         </is>
@@ -7701,7 +6621,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -7715,13 +6635,7 @@
           <t>q17e</t>
         </is>
       </c>
-      <c r="M148" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N148" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R148" t="inlineStr">
+      <c r="O148" t="inlineStr">
         <is>
           <t>q17e</t>
         </is>
@@ -7750,7 +6664,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -7764,13 +6678,7 @@
           <t>q17g</t>
         </is>
       </c>
-      <c r="M149" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N149" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R149" t="inlineStr">
+      <c r="O149" t="inlineStr">
         <is>
           <t>q17g</t>
         </is>
@@ -7799,7 +6707,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -7813,13 +6721,7 @@
           <t>q17i</t>
         </is>
       </c>
-      <c r="M150" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N150" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R150" t="inlineStr">
+      <c r="O150" t="inlineStr">
         <is>
           <t>q17i</t>
         </is>
@@ -7848,7 +6750,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -7862,13 +6764,7 @@
           <t>q17k</t>
         </is>
       </c>
-      <c r="M151" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N151" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R151" t="inlineStr">
+      <c r="O151" t="inlineStr">
         <is>
           <t>q17k</t>
         </is>
@@ -7897,7 +6793,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -7911,13 +6807,7 @@
           <t>q17m</t>
         </is>
       </c>
-      <c r="M152" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N152" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R152" t="inlineStr">
+      <c r="O152" t="inlineStr">
         <is>
           <t>q17m</t>
         </is>
@@ -7946,7 +6836,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -7960,13 +6850,7 @@
           <t>q17o</t>
         </is>
       </c>
-      <c r="M153" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N153" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R153" t="inlineStr">
+      <c r="O153" t="inlineStr">
         <is>
           <t>q17o</t>
         </is>
@@ -7995,7 +6879,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -8009,13 +6893,7 @@
           <t>q17q</t>
         </is>
       </c>
-      <c r="M154" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N154" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R154" t="inlineStr">
+      <c r="O154" t="inlineStr">
         <is>
           <t>q17q</t>
         </is>
@@ -8044,7 +6922,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -8058,13 +6936,7 @@
           <t>q17s</t>
         </is>
       </c>
-      <c r="M155" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N155" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R155" t="inlineStr">
+      <c r="O155" t="inlineStr">
         <is>
           <t>q17s</t>
         </is>
@@ -8093,7 +6965,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -8107,13 +6979,7 @@
           <t>q17u</t>
         </is>
       </c>
-      <c r="M156" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N156" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R156" t="inlineStr">
+      <c r="O156" t="inlineStr">
         <is>
           <t>q17u</t>
         </is>
@@ -8142,7 +7008,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -8156,13 +7022,7 @@
           <t>q180</t>
         </is>
       </c>
-      <c r="M157" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N157" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R157" t="inlineStr">
+      <c r="O157" t="inlineStr">
         <is>
           <t>q180</t>
         </is>
@@ -8191,7 +7051,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -8205,13 +7065,7 @@
           <t>q182</t>
         </is>
       </c>
-      <c r="M158" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N158" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R158" t="inlineStr">
+      <c r="O158" t="inlineStr">
         <is>
           <t>q182</t>
         </is>
@@ -8240,7 +7094,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -8254,13 +7108,7 @@
           <t>q184</t>
         </is>
       </c>
-      <c r="M159" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N159" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R159" t="inlineStr">
+      <c r="O159" t="inlineStr">
         <is>
           <t>q184</t>
         </is>
@@ -8289,7 +7137,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -8303,13 +7151,7 @@
           <t>q186</t>
         </is>
       </c>
-      <c r="M160" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N160" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R160" t="inlineStr">
+      <c r="O160" t="inlineStr">
         <is>
           <t>q186</t>
         </is>
@@ -8338,7 +7180,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -8352,13 +7194,7 @@
           <t>q188</t>
         </is>
       </c>
-      <c r="M161" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N161" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R161" t="inlineStr">
+      <c r="O161" t="inlineStr">
         <is>
           <t>q188</t>
         </is>
@@ -8387,7 +7223,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -8401,13 +7237,7 @@
           <t>q18a</t>
         </is>
       </c>
-      <c r="M162" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N162" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R162" t="inlineStr">
+      <c r="O162" t="inlineStr">
         <is>
           <t>q18a</t>
         </is>
@@ -8436,7 +7266,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -8450,13 +7280,7 @@
           <t>q18c</t>
         </is>
       </c>
-      <c r="M163" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N163" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R163" t="inlineStr">
+      <c r="O163" t="inlineStr">
         <is>
           <t>q18c</t>
         </is>
@@ -8485,7 +7309,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -8499,13 +7323,7 @@
           <t>q18e</t>
         </is>
       </c>
-      <c r="M164" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N164" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R164" t="inlineStr">
+      <c r="O164" t="inlineStr">
         <is>
           <t>q18e</t>
         </is>
@@ -8534,7 +7352,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -8548,13 +7366,7 @@
           <t>q18g</t>
         </is>
       </c>
-      <c r="M165" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N165" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R165" t="inlineStr">
+      <c r="O165" t="inlineStr">
         <is>
           <t>q18g</t>
         </is>
@@ -8583,7 +7395,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -8597,13 +7409,7 @@
           <t>q18i</t>
         </is>
       </c>
-      <c r="M166" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N166" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R166" t="inlineStr">
+      <c r="O166" t="inlineStr">
         <is>
           <t>q18i</t>
         </is>
@@ -8632,7 +7438,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -8646,13 +7452,7 @@
           <t>q18k</t>
         </is>
       </c>
-      <c r="M167" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N167" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R167" t="inlineStr">
+      <c r="O167" t="inlineStr">
         <is>
           <t>q18k</t>
         </is>
@@ -8681,7 +7481,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -8695,13 +7495,7 @@
           <t>q18m</t>
         </is>
       </c>
-      <c r="M168" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N168" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R168" t="inlineStr">
+      <c r="O168" t="inlineStr">
         <is>
           <t>q18m</t>
         </is>
@@ -8730,7 +7524,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -8744,13 +7538,7 @@
           <t>q18o</t>
         </is>
       </c>
-      <c r="M169" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N169" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R169" t="inlineStr">
+      <c r="O169" t="inlineStr">
         <is>
           <t>q18o</t>
         </is>
@@ -8779,7 +7567,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -8793,13 +7581,7 @@
           <t>q18q</t>
         </is>
       </c>
-      <c r="M170" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N170" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R170" t="inlineStr">
+      <c r="O170" t="inlineStr">
         <is>
           <t>q18q</t>
         </is>
@@ -8828,7 +7610,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -8842,13 +7624,7 @@
           <t>q18s</t>
         </is>
       </c>
-      <c r="M171" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N171" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R171" t="inlineStr">
+      <c r="O171" t="inlineStr">
         <is>
           <t>q18s</t>
         </is>
@@ -8877,7 +7653,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -8891,13 +7667,7 @@
           <t>q18u</t>
         </is>
       </c>
-      <c r="M172" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N172" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R172" t="inlineStr">
+      <c r="O172" t="inlineStr">
         <is>
           <t>q18u</t>
         </is>
@@ -8926,7 +7696,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -8940,13 +7710,7 @@
           <t>q190</t>
         </is>
       </c>
-      <c r="M173" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N173" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R173" t="inlineStr">
+      <c r="O173" t="inlineStr">
         <is>
           <t>q190</t>
         </is>
@@ -8975,7 +7739,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -8989,13 +7753,7 @@
           <t>q192</t>
         </is>
       </c>
-      <c r="M174" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N174" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R174" t="inlineStr">
+      <c r="O174" t="inlineStr">
         <is>
           <t>q192</t>
         </is>
@@ -9024,7 +7782,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -9038,13 +7796,7 @@
           <t>q194</t>
         </is>
       </c>
-      <c r="M175" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N175" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R175" t="inlineStr">
+      <c r="O175" t="inlineStr">
         <is>
           <t>q194</t>
         </is>
@@ -9073,7 +7825,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -9087,13 +7839,7 @@
           <t>q196</t>
         </is>
       </c>
-      <c r="M176" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N176" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R176" t="inlineStr">
+      <c r="O176" t="inlineStr">
         <is>
           <t>q196</t>
         </is>
@@ -9122,7 +7868,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -9136,13 +7882,7 @@
           <t>q198</t>
         </is>
       </c>
-      <c r="M177" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N177" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R177" t="inlineStr">
+      <c r="O177" t="inlineStr">
         <is>
           <t>q198</t>
         </is>
@@ -9171,7 +7911,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -9185,13 +7925,7 @@
           <t>q19a</t>
         </is>
       </c>
-      <c r="M178" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N178" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R178" t="inlineStr">
+      <c r="O178" t="inlineStr">
         <is>
           <t>q19a</t>
         </is>
@@ -9220,7 +7954,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -9234,13 +7968,7 @@
           <t>q19c</t>
         </is>
       </c>
-      <c r="M179" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N179" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R179" t="inlineStr">
+      <c r="O179" t="inlineStr">
         <is>
           <t>q19c</t>
         </is>
@@ -9269,7 +7997,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -9283,13 +8011,7 @@
           <t>q19e</t>
         </is>
       </c>
-      <c r="M180" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N180" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R180" t="inlineStr">
+      <c r="O180" t="inlineStr">
         <is>
           <t>q19e</t>
         </is>
@@ -9318,7 +8040,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -9332,13 +8054,7 @@
           <t>q19g</t>
         </is>
       </c>
-      <c r="M181" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N181" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R181" t="inlineStr">
+      <c r="O181" t="inlineStr">
         <is>
           <t>q19g</t>
         </is>
@@ -9367,7 +8083,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -9381,13 +8097,7 @@
           <t>q19i</t>
         </is>
       </c>
-      <c r="M182" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N182" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R182" t="inlineStr">
+      <c r="O182" t="inlineStr">
         <is>
           <t>q19i</t>
         </is>
@@ -9416,7 +8126,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -9430,13 +8140,7 @@
           <t>q19k</t>
         </is>
       </c>
-      <c r="M183" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N183" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R183" t="inlineStr">
+      <c r="O183" t="inlineStr">
         <is>
           <t>q19k</t>
         </is>
@@ -9465,7 +8169,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -9479,13 +8183,7 @@
           <t>q19m</t>
         </is>
       </c>
-      <c r="M184" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N184" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R184" t="inlineStr">
+      <c r="O184" t="inlineStr">
         <is>
           <t>q19m</t>
         </is>
@@ -9514,7 +8212,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -9528,13 +8226,7 @@
           <t>q19o</t>
         </is>
       </c>
-      <c r="M185" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N185" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R185" t="inlineStr">
+      <c r="O185" t="inlineStr">
         <is>
           <t>q19o</t>
         </is>
@@ -9563,7 +8255,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -9577,13 +8269,7 @@
           <t>q19q</t>
         </is>
       </c>
-      <c r="M186" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N186" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R186" t="inlineStr">
+      <c r="O186" t="inlineStr">
         <is>
           <t>q19q</t>
         </is>
@@ -9612,7 +8298,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -9626,13 +8312,7 @@
           <t>q19s</t>
         </is>
       </c>
-      <c r="M187" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N187" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R187" t="inlineStr">
+      <c r="O187" t="inlineStr">
         <is>
           <t>q19s</t>
         </is>
@@ -9661,7 +8341,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -9675,13 +8355,7 @@
           <t>q19u</t>
         </is>
       </c>
-      <c r="M188" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N188" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R188" t="inlineStr">
+      <c r="O188" t="inlineStr">
         <is>
           <t>q19u</t>
         </is>
@@ -9710,7 +8384,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -9724,13 +8398,7 @@
           <t>q1a0</t>
         </is>
       </c>
-      <c r="M189" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N189" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R189" t="inlineStr">
+      <c r="O189" t="inlineStr">
         <is>
           <t>q1a0</t>
         </is>
@@ -9759,7 +8427,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -9773,13 +8441,7 @@
           <t>q1a2</t>
         </is>
       </c>
-      <c r="M190" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N190" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R190" t="inlineStr">
+      <c r="O190" t="inlineStr">
         <is>
           <t>q1a2</t>
         </is>
@@ -9808,7 +8470,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -9822,13 +8484,7 @@
           <t>q1a4</t>
         </is>
       </c>
-      <c r="M191" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N191" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R191" t="inlineStr">
+      <c r="O191" t="inlineStr">
         <is>
           <t>q1a4</t>
         </is>
@@ -9857,7 +8513,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -9871,13 +8527,7 @@
           <t>q1a6</t>
         </is>
       </c>
-      <c r="M192" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N192" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R192" t="inlineStr">
+      <c r="O192" t="inlineStr">
         <is>
           <t>q1a6</t>
         </is>
@@ -9906,7 +8556,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -9920,13 +8570,7 @@
           <t>q1a8</t>
         </is>
       </c>
-      <c r="M193" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N193" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R193" t="inlineStr">
+      <c r="O193" t="inlineStr">
         <is>
           <t>q1a8</t>
         </is>
@@ -9955,7 +8599,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -9969,13 +8613,7 @@
           <t>q1aa</t>
         </is>
       </c>
-      <c r="M194" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N194" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R194" t="inlineStr">
+      <c r="O194" t="inlineStr">
         <is>
           <t>q1aa</t>
         </is>
@@ -10004,7 +8642,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -10018,13 +8656,7 @@
           <t>q1ac</t>
         </is>
       </c>
-      <c r="M195" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N195" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R195" t="inlineStr">
+      <c r="O195" t="inlineStr">
         <is>
           <t>q1ac</t>
         </is>
@@ -10053,7 +8685,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -10067,13 +8699,7 @@
           <t>q1ae</t>
         </is>
       </c>
-      <c r="M196" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N196" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R196" t="inlineStr">
+      <c r="O196" t="inlineStr">
         <is>
           <t>q1ae</t>
         </is>
@@ -10102,7 +8728,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -10116,13 +8742,7 @@
           <t>q1ag</t>
         </is>
       </c>
-      <c r="M197" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N197" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R197" t="inlineStr">
+      <c r="O197" t="inlineStr">
         <is>
           <t>q1ag</t>
         </is>
@@ -10151,7 +8771,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -10165,13 +8785,7 @@
           <t>q1ai</t>
         </is>
       </c>
-      <c r="M198" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N198" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R198" t="inlineStr">
+      <c r="O198" t="inlineStr">
         <is>
           <t>q1ai</t>
         </is>
@@ -10200,7 +8814,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -10214,13 +8828,7 @@
           <t>q1ak</t>
         </is>
       </c>
-      <c r="M199" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N199" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R199" t="inlineStr">
+      <c r="O199" t="inlineStr">
         <is>
           <t>q1ak</t>
         </is>
@@ -10249,7 +8857,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -10263,13 +8871,7 @@
           <t>q1am</t>
         </is>
       </c>
-      <c r="M200" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N200" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R200" t="inlineStr">
+      <c r="O200" t="inlineStr">
         <is>
           <t>q1am</t>
         </is>
@@ -10298,7 +8900,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -10312,13 +8914,7 @@
           <t>q1ao</t>
         </is>
       </c>
-      <c r="M201" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N201" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R201" t="inlineStr">
+      <c r="O201" t="inlineStr">
         <is>
           <t>q1ao</t>
         </is>
@@ -10347,7 +8943,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -10361,13 +8957,7 @@
           <t>q1aq</t>
         </is>
       </c>
-      <c r="M202" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N202" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R202" t="inlineStr">
+      <c r="O202" t="inlineStr">
         <is>
           <t>q1aq</t>
         </is>
@@ -10396,7 +8986,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -10410,13 +9000,7 @@
           <t>q1as</t>
         </is>
       </c>
-      <c r="M203" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N203" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R203" t="inlineStr">
+      <c r="O203" t="inlineStr">
         <is>
           <t>q1as</t>
         </is>
@@ -10445,7 +9029,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -10459,13 +9043,7 @@
           <t>q1au</t>
         </is>
       </c>
-      <c r="M204" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N204" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R204" t="inlineStr">
+      <c r="O204" t="inlineStr">
         <is>
           <t>q1au</t>
         </is>
@@ -10494,7 +9072,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -10508,13 +9086,7 @@
           <t>q1b0</t>
         </is>
       </c>
-      <c r="M205" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N205" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R205" t="inlineStr">
+      <c r="O205" t="inlineStr">
         <is>
           <t>q1b0</t>
         </is>
@@ -10543,7 +9115,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -10557,13 +9129,7 @@
           <t>q1b2</t>
         </is>
       </c>
-      <c r="M206" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N206" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R206" t="inlineStr">
+      <c r="O206" t="inlineStr">
         <is>
           <t>q1b2</t>
         </is>
@@ -10592,7 +9158,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -10606,13 +9172,7 @@
           <t>q1b4</t>
         </is>
       </c>
-      <c r="M207" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N207" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R207" t="inlineStr">
+      <c r="O207" t="inlineStr">
         <is>
           <t>q1b4</t>
         </is>
@@ -10641,7 +9201,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -10655,13 +9215,7 @@
           <t>q1b6</t>
         </is>
       </c>
-      <c r="M208" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N208" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R208" t="inlineStr">
+      <c r="O208" t="inlineStr">
         <is>
           <t>q1b6</t>
         </is>
@@ -10690,7 +9244,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -10704,13 +9258,7 @@
           <t>q1b8</t>
         </is>
       </c>
-      <c r="M209" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N209" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R209" t="inlineStr">
+      <c r="O209" t="inlineStr">
         <is>
           <t>q1b8</t>
         </is>
@@ -10739,7 +9287,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -10753,13 +9301,7 @@
           <t>q1ba</t>
         </is>
       </c>
-      <c r="M210" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N210" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R210" t="inlineStr">
+      <c r="O210" t="inlineStr">
         <is>
           <t>q1ba</t>
         </is>
@@ -10788,7 +9330,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -10802,13 +9344,7 @@
           <t>q1bc</t>
         </is>
       </c>
-      <c r="M211" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N211" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R211" t="inlineStr">
+      <c r="O211" t="inlineStr">
         <is>
           <t>q1bc</t>
         </is>
@@ -10837,7 +9373,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -10851,13 +9387,7 @@
           <t>q1be</t>
         </is>
       </c>
-      <c r="M212" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N212" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R212" t="inlineStr">
+      <c r="O212" t="inlineStr">
         <is>
           <t>q1be</t>
         </is>
@@ -10886,7 +9416,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -10900,13 +9430,7 @@
           <t>q1bg</t>
         </is>
       </c>
-      <c r="M213" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N213" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R213" t="inlineStr">
+      <c r="O213" t="inlineStr">
         <is>
           <t>q1bg</t>
         </is>
@@ -10935,7 +9459,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -10949,13 +9473,7 @@
           <t>q1bi</t>
         </is>
       </c>
-      <c r="M214" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N214" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R214" t="inlineStr">
+      <c r="O214" t="inlineStr">
         <is>
           <t>q1bi</t>
         </is>
@@ -10984,7 +9502,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -10998,13 +9516,7 @@
           <t>q1bk</t>
         </is>
       </c>
-      <c r="M215" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N215" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R215" t="inlineStr">
+      <c r="O215" t="inlineStr">
         <is>
           <t>q1bk</t>
         </is>
@@ -11033,7 +9545,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -11047,13 +9559,7 @@
           <t>q1bm</t>
         </is>
       </c>
-      <c r="M216" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N216" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R216" t="inlineStr">
+      <c r="O216" t="inlineStr">
         <is>
           <t>q1bm</t>
         </is>
@@ -11082,7 +9588,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -11096,13 +9602,7 @@
           <t>q1bo</t>
         </is>
       </c>
-      <c r="M217" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N217" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R217" t="inlineStr">
+      <c r="O217" t="inlineStr">
         <is>
           <t>q1bo</t>
         </is>
@@ -11131,7 +9631,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -11145,13 +9645,7 @@
           <t>q1bq</t>
         </is>
       </c>
-      <c r="M218" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N218" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R218" t="inlineStr">
+      <c r="O218" t="inlineStr">
         <is>
           <t>q1bq</t>
         </is>
@@ -11180,7 +9674,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -11194,13 +9688,7 @@
           <t>q1bs</t>
         </is>
       </c>
-      <c r="M219" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N219" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R219" t="inlineStr">
+      <c r="O219" t="inlineStr">
         <is>
           <t>q1bs</t>
         </is>
@@ -11229,7 +9717,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -11243,13 +9731,7 @@
           <t>q1bu</t>
         </is>
       </c>
-      <c r="M220" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N220" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R220" t="inlineStr">
+      <c r="O220" t="inlineStr">
         <is>
           <t>q1bu</t>
         </is>
@@ -11278,7 +9760,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -11292,13 +9774,7 @@
           <t>q1c0</t>
         </is>
       </c>
-      <c r="M221" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N221" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R221" t="inlineStr">
+      <c r="O221" t="inlineStr">
         <is>
           <t>q1c0</t>
         </is>
@@ -11327,7 +9803,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -11341,13 +9817,7 @@
           <t>q1c2</t>
         </is>
       </c>
-      <c r="M222" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N222" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R222" t="inlineStr">
+      <c r="O222" t="inlineStr">
         <is>
           <t>q1c2</t>
         </is>
@@ -11376,7 +9846,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -11390,13 +9860,7 @@
           <t>q1c4</t>
         </is>
       </c>
-      <c r="M223" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N223" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R223" t="inlineStr">
+      <c r="O223" t="inlineStr">
         <is>
           <t>q1c4</t>
         </is>
@@ -11425,7 +9889,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -11439,13 +9903,7 @@
           <t>q1c6</t>
         </is>
       </c>
-      <c r="M224" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N224" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R224" t="inlineStr">
+      <c r="O224" t="inlineStr">
         <is>
           <t>q1c6</t>
         </is>
@@ -11474,7 +9932,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -11488,13 +9946,7 @@
           <t>q1c8</t>
         </is>
       </c>
-      <c r="M225" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N225" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R225" t="inlineStr">
+      <c r="O225" t="inlineStr">
         <is>
           <t>q1c8</t>
         </is>
@@ -11523,7 +9975,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -11537,13 +9989,7 @@
           <t>q1ca</t>
         </is>
       </c>
-      <c r="M226" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N226" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R226" t="inlineStr">
+      <c r="O226" t="inlineStr">
         <is>
           <t>q1ca</t>
         </is>
@@ -11572,7 +10018,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -11586,13 +10032,7 @@
           <t>q1cc</t>
         </is>
       </c>
-      <c r="M227" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N227" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R227" t="inlineStr">
+      <c r="O227" t="inlineStr">
         <is>
           <t>q1cc</t>
         </is>
@@ -11621,7 +10061,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -11635,13 +10075,7 @@
           <t>q1ce</t>
         </is>
       </c>
-      <c r="M228" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N228" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R228" t="inlineStr">
+      <c r="O228" t="inlineStr">
         <is>
           <t>q1ce</t>
         </is>
@@ -11670,7 +10104,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -11684,13 +10118,7 @@
           <t>q1cg</t>
         </is>
       </c>
-      <c r="M229" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N229" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R229" t="inlineStr">
+      <c r="O229" t="inlineStr">
         <is>
           <t>q1cg</t>
         </is>
@@ -11719,7 +10147,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -11733,13 +10161,7 @@
           <t>q1ci</t>
         </is>
       </c>
-      <c r="M230" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N230" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R230" t="inlineStr">
+      <c r="O230" t="inlineStr">
         <is>
           <t>q1ci</t>
         </is>
@@ -11768,7 +10190,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -11782,13 +10204,7 @@
           <t>q1ck</t>
         </is>
       </c>
-      <c r="M231" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N231" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R231" t="inlineStr">
+      <c r="O231" t="inlineStr">
         <is>
           <t>q1ck</t>
         </is>
@@ -11817,7 +10233,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -11831,13 +10247,7 @@
           <t>q1cm</t>
         </is>
       </c>
-      <c r="M232" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N232" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R232" t="inlineStr">
+      <c r="O232" t="inlineStr">
         <is>
           <t>q1cm</t>
         </is>
@@ -11866,7 +10276,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -11880,13 +10290,7 @@
           <t>q1co</t>
         </is>
       </c>
-      <c r="M233" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N233" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R233" t="inlineStr">
+      <c r="O233" t="inlineStr">
         <is>
           <t>q1co</t>
         </is>
@@ -11915,7 +10319,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -11929,13 +10333,7 @@
           <t>q1cq</t>
         </is>
       </c>
-      <c r="M234" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N234" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R234" t="inlineStr">
+      <c r="O234" t="inlineStr">
         <is>
           <t>q1cq</t>
         </is>
@@ -11964,7 +10362,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -11978,13 +10376,7 @@
           <t>q1cs</t>
         </is>
       </c>
-      <c r="M235" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N235" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R235" t="inlineStr">
+      <c r="O235" t="inlineStr">
         <is>
           <t>q1cs</t>
         </is>
@@ -12013,7 +10405,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -12027,13 +10419,7 @@
           <t>q1cu</t>
         </is>
       </c>
-      <c r="M236" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N236" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R236" t="inlineStr">
+      <c r="O236" t="inlineStr">
         <is>
           <t>q1cu</t>
         </is>
@@ -12062,7 +10448,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -12076,13 +10462,7 @@
           <t>q1d0</t>
         </is>
       </c>
-      <c r="M237" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N237" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R237" t="inlineStr">
+      <c r="O237" t="inlineStr">
         <is>
           <t>q1d0</t>
         </is>
@@ -12111,7 +10491,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -12125,13 +10505,7 @@
           <t>q1d2</t>
         </is>
       </c>
-      <c r="M238" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N238" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R238" t="inlineStr">
+      <c r="O238" t="inlineStr">
         <is>
           <t>q1d2</t>
         </is>
@@ -12160,7 +10534,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -12174,13 +10548,7 @@
           <t>q1d4</t>
         </is>
       </c>
-      <c r="M239" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N239" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R239" t="inlineStr">
+      <c r="O239" t="inlineStr">
         <is>
           <t>q1d4</t>
         </is>
@@ -12209,7 +10577,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -12223,13 +10591,7 @@
           <t>q1d6</t>
         </is>
       </c>
-      <c r="M240" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N240" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R240" t="inlineStr">
+      <c r="O240" t="inlineStr">
         <is>
           <t>q1d6</t>
         </is>
@@ -12258,7 +10620,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -12272,13 +10634,7 @@
           <t>q1d8</t>
         </is>
       </c>
-      <c r="M241" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N241" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R241" t="inlineStr">
+      <c r="O241" t="inlineStr">
         <is>
           <t>q1d8</t>
         </is>
@@ -12307,7 +10663,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -12321,13 +10677,7 @@
           <t>q1da</t>
         </is>
       </c>
-      <c r="M242" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N242" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R242" t="inlineStr">
+      <c r="O242" t="inlineStr">
         <is>
           <t>q1da</t>
         </is>
@@ -12356,7 +10706,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -12370,13 +10720,7 @@
           <t>q1dc</t>
         </is>
       </c>
-      <c r="M243" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N243" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R243" t="inlineStr">
+      <c r="O243" t="inlineStr">
         <is>
           <t>q1dc</t>
         </is>
@@ -12405,7 +10749,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -12419,13 +10763,7 @@
           <t>q1de</t>
         </is>
       </c>
-      <c r="M244" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N244" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R244" t="inlineStr">
+      <c r="O244" t="inlineStr">
         <is>
           <t>q1de</t>
         </is>
@@ -12454,7 +10792,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -12468,13 +10806,7 @@
           <t>q1dg</t>
         </is>
       </c>
-      <c r="M245" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N245" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R245" t="inlineStr">
+      <c r="O245" t="inlineStr">
         <is>
           <t>q1dg</t>
         </is>
@@ -12503,7 +10835,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -12517,13 +10849,7 @@
           <t>q1di</t>
         </is>
       </c>
-      <c r="M246" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N246" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R246" t="inlineStr">
+      <c r="O246" t="inlineStr">
         <is>
           <t>q1di</t>
         </is>
@@ -12552,7 +10878,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -12566,13 +10892,7 @@
           <t>q1dk</t>
         </is>
       </c>
-      <c r="M247" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N247" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R247" t="inlineStr">
+      <c r="O247" t="inlineStr">
         <is>
           <t>q1dk</t>
         </is>
@@ -12601,7 +10921,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -12615,13 +10935,7 @@
           <t>q1dm</t>
         </is>
       </c>
-      <c r="M248" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N248" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R248" t="inlineStr">
+      <c r="O248" t="inlineStr">
         <is>
           <t>q1dm</t>
         </is>
@@ -12650,7 +10964,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -12664,13 +10978,7 @@
           <t>q1do</t>
         </is>
       </c>
-      <c r="M249" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N249" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R249" t="inlineStr">
+      <c r="O249" t="inlineStr">
         <is>
           <t>q1do</t>
         </is>
@@ -12699,7 +11007,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -12713,13 +11021,7 @@
           <t>q1dq</t>
         </is>
       </c>
-      <c r="M250" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N250" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R250" t="inlineStr">
+      <c r="O250" t="inlineStr">
         <is>
           <t>q1dq</t>
         </is>
@@ -12748,7 +11050,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -12762,13 +11064,7 @@
           <t>q1ds</t>
         </is>
       </c>
-      <c r="M251" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N251" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R251" t="inlineStr">
+      <c r="O251" t="inlineStr">
         <is>
           <t>q1ds</t>
         </is>
@@ -12797,7 +11093,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -12811,13 +11107,7 @@
           <t>q1du</t>
         </is>
       </c>
-      <c r="M252" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N252" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R252" t="inlineStr">
+      <c r="O252" t="inlineStr">
         <is>
           <t>q1du</t>
         </is>
@@ -12846,7 +11136,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -12860,13 +11150,7 @@
           <t>q1e0</t>
         </is>
       </c>
-      <c r="M253" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N253" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R253" t="inlineStr">
+      <c r="O253" t="inlineStr">
         <is>
           <t>q1e0</t>
         </is>
@@ -12895,7 +11179,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -12909,13 +11193,7 @@
           <t>q1e2</t>
         </is>
       </c>
-      <c r="M254" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N254" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R254" t="inlineStr">
+      <c r="O254" t="inlineStr">
         <is>
           <t>q1e2</t>
         </is>
@@ -12944,7 +11222,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -12958,13 +11236,7 @@
           <t>q1e4</t>
         </is>
       </c>
-      <c r="M255" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N255" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R255" t="inlineStr">
+      <c r="O255" t="inlineStr">
         <is>
           <t>q1e4</t>
         </is>
@@ -12993,7 +11265,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -13007,13 +11279,7 @@
           <t>q1e6</t>
         </is>
       </c>
-      <c r="M256" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N256" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R256" t="inlineStr">
+      <c r="O256" t="inlineStr">
         <is>
           <t>q1e6</t>
         </is>
@@ -13042,7 +11308,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -13056,13 +11322,7 @@
           <t>q1e8</t>
         </is>
       </c>
-      <c r="M257" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N257" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R257" t="inlineStr">
+      <c r="O257" t="inlineStr">
         <is>
           <t>q1e8</t>
         </is>
@@ -13091,7 +11351,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -13105,13 +11365,7 @@
           <t>q1ea</t>
         </is>
       </c>
-      <c r="M258" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N258" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R258" t="inlineStr">
+      <c r="O258" t="inlineStr">
         <is>
           <t>q1ea</t>
         </is>
@@ -13140,7 +11394,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -13154,13 +11408,7 @@
           <t>q1ec</t>
         </is>
       </c>
-      <c r="M259" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N259" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R259" t="inlineStr">
+      <c r="O259" t="inlineStr">
         <is>
           <t>q1ec</t>
         </is>
@@ -13189,7 +11437,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -13203,13 +11451,7 @@
           <t>q1ee</t>
         </is>
       </c>
-      <c r="M260" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N260" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R260" t="inlineStr">
+      <c r="O260" t="inlineStr">
         <is>
           <t>q1ee</t>
         </is>
@@ -13238,7 +11480,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -13252,13 +11494,7 @@
           <t>q1eg</t>
         </is>
       </c>
-      <c r="M261" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N261" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R261" t="inlineStr">
+      <c r="O261" t="inlineStr">
         <is>
           <t>q1eg</t>
         </is>
@@ -13287,7 +11523,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -13301,13 +11537,7 @@
           <t>q1ei</t>
         </is>
       </c>
-      <c r="M262" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N262" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R262" t="inlineStr">
+      <c r="O262" t="inlineStr">
         <is>
           <t>q1ei</t>
         </is>
@@ -13336,7 +11566,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -13350,13 +11580,7 @@
           <t>q1ek</t>
         </is>
       </c>
-      <c r="M263" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N263" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R263" t="inlineStr">
+      <c r="O263" t="inlineStr">
         <is>
           <t>q1ek</t>
         </is>
@@ -13385,7 +11609,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -13399,13 +11623,7 @@
           <t>q1em</t>
         </is>
       </c>
-      <c r="M264" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N264" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R264" t="inlineStr">
+      <c r="O264" t="inlineStr">
         <is>
           <t>q1em</t>
         </is>
@@ -13434,7 +11652,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -13448,13 +11666,7 @@
           <t>q1eo</t>
         </is>
       </c>
-      <c r="M265" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N265" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R265" t="inlineStr">
+      <c r="O265" t="inlineStr">
         <is>
           <t>q1eo</t>
         </is>
@@ -13483,7 +11695,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -13497,13 +11709,7 @@
           <t>q1eq</t>
         </is>
       </c>
-      <c r="M266" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N266" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R266" t="inlineStr">
+      <c r="O266" t="inlineStr">
         <is>
           <t>q1eq</t>
         </is>
@@ -13532,7 +11738,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -13546,13 +11752,7 @@
           <t>q1es</t>
         </is>
       </c>
-      <c r="M267" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N267" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R267" t="inlineStr">
+      <c r="O267" t="inlineStr">
         <is>
           <t>q1es</t>
         </is>
@@ -13581,7 +11781,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -13595,13 +11795,7 @@
           <t>q1eu</t>
         </is>
       </c>
-      <c r="M268" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N268" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R268" t="inlineStr">
+      <c r="O268" t="inlineStr">
         <is>
           <t>q1eu</t>
         </is>
@@ -13630,7 +11824,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -13644,13 +11838,7 @@
           <t>q1f0</t>
         </is>
       </c>
-      <c r="M269" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N269" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R269" t="inlineStr">
+      <c r="O269" t="inlineStr">
         <is>
           <t>q1f0</t>
         </is>
@@ -13679,7 +11867,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -13693,13 +11881,7 @@
           <t>q1f2</t>
         </is>
       </c>
-      <c r="M270" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N270" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R270" t="inlineStr">
+      <c r="O270" t="inlineStr">
         <is>
           <t>q1f2</t>
         </is>
@@ -13728,7 +11910,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -13742,13 +11924,7 @@
           <t>q1f4</t>
         </is>
       </c>
-      <c r="M271" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N271" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R271" t="inlineStr">
+      <c r="O271" t="inlineStr">
         <is>
           <t>q1f4</t>
         </is>
@@ -13777,7 +11953,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -13791,13 +11967,7 @@
           <t>q1f6</t>
         </is>
       </c>
-      <c r="M272" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N272" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R272" t="inlineStr">
+      <c r="O272" t="inlineStr">
         <is>
           <t>q1f6</t>
         </is>
@@ -13826,7 +11996,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -13840,13 +12010,7 @@
           <t>q1f8</t>
         </is>
       </c>
-      <c r="M273" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N273" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R273" t="inlineStr">
+      <c r="O273" t="inlineStr">
         <is>
           <t>q1f8</t>
         </is>
@@ -13875,7 +12039,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -13889,13 +12053,7 @@
           <t>q1fa</t>
         </is>
       </c>
-      <c r="M274" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N274" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R274" t="inlineStr">
+      <c r="O274" t="inlineStr">
         <is>
           <t>q1fa</t>
         </is>
@@ -13924,7 +12082,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -13938,13 +12096,7 @@
           <t>q1fc</t>
         </is>
       </c>
-      <c r="M275" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N275" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R275" t="inlineStr">
+      <c r="O275" t="inlineStr">
         <is>
           <t>q1fc</t>
         </is>
@@ -13973,7 +12125,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -13987,13 +12139,7 @@
           <t>q1fe</t>
         </is>
       </c>
-      <c r="M276" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N276" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R276" t="inlineStr">
+      <c r="O276" t="inlineStr">
         <is>
           <t>q1fe</t>
         </is>
@@ -14022,7 +12168,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -14036,13 +12182,7 @@
           <t>q1fg</t>
         </is>
       </c>
-      <c r="M277" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N277" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R277" t="inlineStr">
+      <c r="O277" t="inlineStr">
         <is>
           <t>q1fg</t>
         </is>
@@ -14071,7 +12211,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -14085,13 +12225,7 @@
           <t>q1fi</t>
         </is>
       </c>
-      <c r="M278" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N278" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R278" t="inlineStr">
+      <c r="O278" t="inlineStr">
         <is>
           <t>q1fi</t>
         </is>
@@ -14120,7 +12254,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -14134,13 +12268,7 @@
           <t>q1fk</t>
         </is>
       </c>
-      <c r="M279" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N279" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R279" t="inlineStr">
+      <c r="O279" t="inlineStr">
         <is>
           <t>q1fk</t>
         </is>
@@ -14169,7 +12297,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -14183,13 +12311,7 @@
           <t>q1fm</t>
         </is>
       </c>
-      <c r="M280" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N280" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R280" t="inlineStr">
+      <c r="O280" t="inlineStr">
         <is>
           <t>q1fm</t>
         </is>
@@ -14218,7 +12340,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -14232,13 +12354,7 @@
           <t>q1fo</t>
         </is>
       </c>
-      <c r="M281" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N281" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R281" t="inlineStr">
+      <c r="O281" t="inlineStr">
         <is>
           <t>q1fo</t>
         </is>
@@ -14267,7 +12383,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -14281,13 +12397,7 @@
           <t>q1fq</t>
         </is>
       </c>
-      <c r="M282" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N282" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R282" t="inlineStr">
+      <c r="O282" t="inlineStr">
         <is>
           <t>q1fq</t>
         </is>
@@ -14316,7 +12426,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -14330,13 +12440,7 @@
           <t>q1fs</t>
         </is>
       </c>
-      <c r="M283" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N283" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R283" t="inlineStr">
+      <c r="O283" t="inlineStr">
         <is>
           <t>q1fs</t>
         </is>
@@ -14365,7 +12469,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -14379,13 +12483,7 @@
           <t>q1fu</t>
         </is>
       </c>
-      <c r="M284" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N284" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R284" t="inlineStr">
+      <c r="O284" t="inlineStr">
         <is>
           <t>q1fu</t>
         </is>
@@ -14414,7 +12512,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -14428,13 +12526,7 @@
           <t>q1g0</t>
         </is>
       </c>
-      <c r="M285" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N285" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R285" t="inlineStr">
+      <c r="O285" t="inlineStr">
         <is>
           <t>q1g0</t>
         </is>
@@ -14463,7 +12555,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -14477,13 +12569,7 @@
           <t>q1g2</t>
         </is>
       </c>
-      <c r="M286" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N286" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R286" t="inlineStr">
+      <c r="O286" t="inlineStr">
         <is>
           <t>q1g2</t>
         </is>
@@ -14512,7 +12598,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -14526,13 +12612,7 @@
           <t>q1g4</t>
         </is>
       </c>
-      <c r="M287" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N287" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R287" t="inlineStr">
+      <c r="O287" t="inlineStr">
         <is>
           <t>q1g4</t>
         </is>
@@ -14561,7 +12641,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -14575,13 +12655,7 @@
           <t>q1g6</t>
         </is>
       </c>
-      <c r="M288" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N288" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R288" t="inlineStr">
+      <c r="O288" t="inlineStr">
         <is>
           <t>q1g6</t>
         </is>
@@ -14610,7 +12684,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -14624,13 +12698,7 @@
           <t>q1g8</t>
         </is>
       </c>
-      <c r="M289" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N289" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R289" t="inlineStr">
+      <c r="O289" t="inlineStr">
         <is>
           <t>q1g8</t>
         </is>
@@ -14659,7 +12727,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -14673,13 +12741,7 @@
           <t>q1ga</t>
         </is>
       </c>
-      <c r="M290" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N290" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R290" t="inlineStr">
+      <c r="O290" t="inlineStr">
         <is>
           <t>q1ga</t>
         </is>
@@ -14708,7 +12770,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -14722,13 +12784,7 @@
           <t>q1gc</t>
         </is>
       </c>
-      <c r="M291" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N291" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R291" t="inlineStr">
+      <c r="O291" t="inlineStr">
         <is>
           <t>q1gc</t>
         </is>
@@ -14757,7 +12813,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -14771,13 +12827,7 @@
           <t>q1ge</t>
         </is>
       </c>
-      <c r="M292" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N292" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R292" t="inlineStr">
+      <c r="O292" t="inlineStr">
         <is>
           <t>q1ge</t>
         </is>
@@ -14806,7 +12856,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -14820,13 +12870,7 @@
           <t>q1gg</t>
         </is>
       </c>
-      <c r="M293" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N293" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R293" t="inlineStr">
+      <c r="O293" t="inlineStr">
         <is>
           <t>q1gg</t>
         </is>
@@ -14855,7 +12899,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -14869,13 +12913,7 @@
           <t>q1gi</t>
         </is>
       </c>
-      <c r="M294" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N294" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R294" t="inlineStr">
+      <c r="O294" t="inlineStr">
         <is>
           <t>q1gi</t>
         </is>
@@ -14904,7 +12942,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -14918,13 +12956,7 @@
           <t>q1gk</t>
         </is>
       </c>
-      <c r="M295" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N295" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R295" t="inlineStr">
+      <c r="O295" t="inlineStr">
         <is>
           <t>q1gk</t>
         </is>
@@ -14953,7 +12985,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -14967,13 +12999,7 @@
           <t>q1gm</t>
         </is>
       </c>
-      <c r="M296" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N296" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R296" t="inlineStr">
+      <c r="O296" t="inlineStr">
         <is>
           <t>q1gm</t>
         </is>
@@ -15002,7 +13028,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -15016,13 +13042,7 @@
           <t>q1go</t>
         </is>
       </c>
-      <c r="M297" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N297" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R297" t="inlineStr">
+      <c r="O297" t="inlineStr">
         <is>
           <t>q1go</t>
         </is>
@@ -15051,7 +13071,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -15065,13 +13085,7 @@
           <t>q1gq</t>
         </is>
       </c>
-      <c r="M298" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N298" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R298" t="inlineStr">
+      <c r="O298" t="inlineStr">
         <is>
           <t>q1gq</t>
         </is>
@@ -15100,7 +13114,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -15114,13 +13128,7 @@
           <t>q1gs</t>
         </is>
       </c>
-      <c r="M299" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N299" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R299" t="inlineStr">
+      <c r="O299" t="inlineStr">
         <is>
           <t>q1gs</t>
         </is>
@@ -15149,7 +13157,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -15163,13 +13171,7 @@
           <t>q1gu</t>
         </is>
       </c>
-      <c r="M300" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N300" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R300" t="inlineStr">
+      <c r="O300" t="inlineStr">
         <is>
           <t>q1gu</t>
         </is>
@@ -15198,7 +13200,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -15212,13 +13214,7 @@
           <t>q1h0</t>
         </is>
       </c>
-      <c r="M301" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N301" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R301" t="inlineStr">
+      <c r="O301" t="inlineStr">
         <is>
           <t>q1h0</t>
         </is>
@@ -15247,7 +13243,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -15261,13 +13257,7 @@
           <t>q1h2</t>
         </is>
       </c>
-      <c r="M302" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N302" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R302" t="inlineStr">
+      <c r="O302" t="inlineStr">
         <is>
           <t>q1h2</t>
         </is>
@@ -15296,7 +13286,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -15310,13 +13300,7 @@
           <t>q1h4</t>
         </is>
       </c>
-      <c r="M303" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N303" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R303" t="inlineStr">
+      <c r="O303" t="inlineStr">
         <is>
           <t>q1h4</t>
         </is>
@@ -15345,7 +13329,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -15359,13 +13343,7 @@
           <t>q1h6</t>
         </is>
       </c>
-      <c r="M304" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N304" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R304" t="inlineStr">
+      <c r="O304" t="inlineStr">
         <is>
           <t>q1h6</t>
         </is>
@@ -15394,7 +13372,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -15408,13 +13386,7 @@
           <t>q1h8</t>
         </is>
       </c>
-      <c r="M305" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N305" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R305" t="inlineStr">
+      <c r="O305" t="inlineStr">
         <is>
           <t>q1h8</t>
         </is>
@@ -15443,7 +13415,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -15457,13 +13429,7 @@
           <t>q1ha</t>
         </is>
       </c>
-      <c r="M306" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N306" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R306" t="inlineStr">
+      <c r="O306" t="inlineStr">
         <is>
           <t>q1ha</t>
         </is>
@@ -15492,7 +13458,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -15506,13 +13472,7 @@
           <t>q1hc</t>
         </is>
       </c>
-      <c r="M307" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N307" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R307" t="inlineStr">
+      <c r="O307" t="inlineStr">
         <is>
           <t>q1hc</t>
         </is>
@@ -15541,7 +13501,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -15555,13 +13515,7 @@
           <t>q1he</t>
         </is>
       </c>
-      <c r="M308" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N308" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R308" t="inlineStr">
+      <c r="O308" t="inlineStr">
         <is>
           <t>q1he</t>
         </is>
@@ -15590,7 +13544,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -15604,13 +13558,7 @@
           <t>q1hg</t>
         </is>
       </c>
-      <c r="M309" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N309" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R309" t="inlineStr">
+      <c r="O309" t="inlineStr">
         <is>
           <t>q1hg</t>
         </is>
@@ -15639,7 +13587,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -15653,13 +13601,7 @@
           <t>q1hi</t>
         </is>
       </c>
-      <c r="M310" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N310" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R310" t="inlineStr">
+      <c r="O310" t="inlineStr">
         <is>
           <t>q1hi</t>
         </is>
@@ -15688,7 +13630,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -15702,13 +13644,7 @@
           <t>q1hk</t>
         </is>
       </c>
-      <c r="M311" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N311" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R311" t="inlineStr">
+      <c r="O311" t="inlineStr">
         <is>
           <t>q1hk</t>
         </is>
@@ -15737,7 +13673,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -15751,13 +13687,7 @@
           <t>q1hm</t>
         </is>
       </c>
-      <c r="M312" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N312" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R312" t="inlineStr">
+      <c r="O312" t="inlineStr">
         <is>
           <t>q1hm</t>
         </is>
@@ -15786,7 +13716,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -15800,13 +13730,7 @@
           <t>q1ho</t>
         </is>
       </c>
-      <c r="M313" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N313" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R313" t="inlineStr">
+      <c r="O313" t="inlineStr">
         <is>
           <t>q1ho</t>
         </is>
@@ -15835,7 +13759,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -15849,13 +13773,7 @@
           <t>q1hq</t>
         </is>
       </c>
-      <c r="M314" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N314" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R314" t="inlineStr">
+      <c r="O314" t="inlineStr">
         <is>
           <t>q1hq</t>
         </is>
@@ -15884,7 +13802,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -15898,13 +13816,7 @@
           <t>q1hs</t>
         </is>
       </c>
-      <c r="M315" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N315" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R315" t="inlineStr">
+      <c r="O315" t="inlineStr">
         <is>
           <t>q1hs</t>
         </is>
@@ -15933,7 +13845,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -15947,13 +13859,7 @@
           <t>q1hu</t>
         </is>
       </c>
-      <c r="M316" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N316" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R316" t="inlineStr">
+      <c r="O316" t="inlineStr">
         <is>
           <t>q1hu</t>
         </is>
@@ -15982,7 +13888,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">    </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -15996,13 +13902,7 @@
           <t>q1i0</t>
         </is>
       </c>
-      <c r="M317" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="N317" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="R317" t="inlineStr">
+      <c r="O317" t="inlineStr">
         <is>
           <t>q1i0</t>
         </is>
